--- a/QLNS/bin/Debug/FileExcels/BC_MangLuoiLD_02_03_04_07_TCCB.xlsx
+++ b/QLNS/bin/Debug/FileExcels/BC_MangLuoiLD_02_03_04_07_TCCB.xlsx
@@ -12,7 +12,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'07-BC-TCCB'!$7:$9</definedName>
   </definedNames>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="145621" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -451,7 +451,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -498,10 +498,31 @@
     <xf numFmtId="4" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -516,26 +537,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -870,168 +873,168 @@
       </c>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
+      <c r="B2" s="16"/>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="27"/>
-      <c r="N2" s="27"/>
-      <c r="O2" s="27"/>
-      <c r="P2" s="27"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="27"/>
-      <c r="S2" s="27"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="27"/>
+      <c r="M2" s="16"/>
+      <c r="N2" s="16"/>
+      <c r="O2" s="16"/>
+      <c r="P2" s="16"/>
+      <c r="Q2" s="16"/>
+      <c r="R2" s="16"/>
+      <c r="S2" s="16"/>
+      <c r="T2" s="16"/>
+      <c r="U2" s="16"/>
     </row>
     <row r="3" spans="1:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
-      <c r="L3" s="28" t="s">
+      <c r="L3" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="28"/>
-      <c r="N3" s="28"/>
-      <c r="O3" s="28"/>
-      <c r="P3" s="28"/>
-      <c r="Q3" s="28"/>
-      <c r="R3" s="28"/>
-      <c r="S3" s="28"/>
-      <c r="T3" s="28"/>
-      <c r="U3" s="28"/>
+      <c r="M3" s="17"/>
+      <c r="N3" s="17"/>
+      <c r="O3" s="17"/>
+      <c r="P3" s="17"/>
+      <c r="Q3" s="17"/>
+      <c r="R3" s="17"/>
+      <c r="S3" s="17"/>
+      <c r="T3" s="17"/>
+      <c r="U3" s="17"/>
     </row>
     <row r="4" spans="1:21" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="B4" s="27"/>
-      <c r="C4" s="27"/>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="27"/>
-      <c r="J4" s="27"/>
-      <c r="K4" s="27"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="27"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
-      <c r="S4" s="27"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="27"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
+      <c r="N4" s="16"/>
+      <c r="O4" s="16"/>
+      <c r="P4" s="16"/>
+      <c r="Q4" s="16"/>
+      <c r="R4" s="16"/>
+      <c r="S4" s="16"/>
+      <c r="T4" s="16"/>
+      <c r="U4" s="16"/>
     </row>
     <row r="5" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="27"/>
-      <c r="E5" s="27"/>
-      <c r="F5" s="27"/>
-      <c r="G5" s="27"/>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="16"/>
+      <c r="N5" s="16"/>
+      <c r="O5" s="16"/>
+      <c r="P5" s="16"/>
+      <c r="Q5" s="16"/>
+      <c r="R5" s="16"/>
+      <c r="S5" s="16"/>
+      <c r="T5" s="16"/>
+      <c r="U5" s="16"/>
     </row>
     <row r="6" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:21" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="16" t="s">
+      <c r="C7" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="18" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="22"/>
       <c r="G7" s="22"/>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="18" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="23" t="s">
         <v>13</v>
       </c>
       <c r="J7" s="24"/>
-      <c r="K7" s="16" t="s">
+      <c r="K7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="L7" s="16" t="s">
+      <c r="L7" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="N7" s="16" t="s">
+      <c r="N7" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="O7" s="16" t="s">
+      <c r="O7" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="P7" s="16" t="s">
+      <c r="P7" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="Q7" s="16" t="s">
+      <c r="Q7" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="R7" s="16"/>
-      <c r="S7" s="18" t="s">
+      <c r="R7" s="18"/>
+      <c r="S7" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="T7" s="18" t="s">
+      <c r="T7" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="U7" s="20" t="s">
+      <c r="U7" s="27" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="6" customFormat="1" ht="132" x14ac:dyDescent="0.3">
-      <c r="A8" s="17"/>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="26"/>
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="21"/>
       <c r="E8" s="10" t="s">
         <v>9</v>
       </c>
@@ -1048,21 +1051,21 @@
       <c r="J8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="17"/>
-      <c r="M8" s="17"/>
-      <c r="N8" s="17"/>
-      <c r="O8" s="17"/>
-      <c r="P8" s="17"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="19"/>
+      <c r="M8" s="19"/>
+      <c r="N8" s="19"/>
+      <c r="O8" s="19"/>
+      <c r="P8" s="19"/>
       <c r="Q8" s="10" t="s">
         <v>55</v>
       </c>
       <c r="R8" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="S8" s="19"/>
-      <c r="T8" s="19"/>
-      <c r="U8" s="21"/>
+      <c r="S8" s="26"/>
+      <c r="T8" s="26"/>
+      <c r="U8" s="28"/>
     </row>
     <row r="9" spans="1:21" s="13" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
@@ -1187,7 +1190,7 @@
       <c r="S10" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="T10" s="9" t="s">
+      <c r="T10" s="29" t="s">
         <v>67</v>
       </c>
       <c r="U10" s="14" t="s">
@@ -1196,29 +1199,29 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:G7"/>
     <mergeCell ref="L2:U2"/>
     <mergeCell ref="L3:U3"/>
     <mergeCell ref="A4:U4"/>
     <mergeCell ref="A5:U5"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="T7:T8"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.6" right="0.5" top="0.6" bottom="0.5" header="0.05" footer="0.05"/>

--- a/QLNS/bin/Debug/FileExcels/BC_MangLuoiLD_02_03_04_07_TCCB.xlsx
+++ b/QLNS/bin/Debug/FileExcels/BC_MangLuoiLD_02_03_04_07_TCCB.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VBSP_DEV\AZUREDEPOPS_PROJECT\VBSP-QLNS\VBSP-QLNS\QLNS\FileExcels\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="15360" windowHeight="6468" tabRatio="695"/>
   </bookViews>
@@ -12,7 +17,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'07-BC-TCCB'!$7:$9</definedName>
   </definedNames>
-  <calcPr calcId="145621" calcMode="manual"/>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
@@ -37,9 +42,6 @@
     <t xml:space="preserve">Tên đơn vị </t>
   </si>
   <si>
-    <t>Số khách hàng</t>
-  </si>
-  <si>
     <t>Định biên</t>
   </si>
   <si>
@@ -50,12 +52,6 @@
   </si>
   <si>
     <t>Lao động CMNV thực hiện tháng trước</t>
-  </si>
-  <si>
-    <t>Điểm giao dịch xã</t>
-  </si>
-  <si>
-    <t>Số xã, phường,  thị trấn</t>
   </si>
   <si>
     <t>Trong đó</t>
@@ -233,6 +229,15 @@
   </si>
   <si>
     <t>Mẫu số 04/BC-TCCB</t>
+  </si>
+  <si>
+    <t>Điểm giao dịch</t>
+  </si>
+  <si>
+    <t>Số xã, phường,  đặc khu</t>
+  </si>
+  <si>
+    <t>Số khách hàng (KH dư nợ và KH có tiền gửi)</t>
   </si>
 </sst>
 </file>
@@ -498,47 +503,47 @@
     <xf numFmtId="4" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="7" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -601,7 +606,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -636,7 +641,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -869,359 +874,359 @@
     <row r="1" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="T1" s="1"/>
       <c r="U1" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="F2" s="4"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
-      <c r="L2" s="16" t="s">
+      <c r="L2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="M2" s="16"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16"/>
-      <c r="Q2" s="16"/>
-      <c r="R2" s="16"/>
-      <c r="S2" s="16"/>
-      <c r="T2" s="16"/>
-      <c r="U2" s="16"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
+      <c r="Q2" s="28"/>
+      <c r="R2" s="28"/>
+      <c r="S2" s="28"/>
+      <c r="T2" s="28"/>
+      <c r="U2" s="28"/>
     </row>
     <row r="3" spans="1:21" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="A3" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
-      <c r="L3" s="17" t="s">
+      <c r="L3" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
-      <c r="Q3" s="17"/>
-      <c r="R3" s="17"/>
-      <c r="S3" s="17"/>
-      <c r="T3" s="17"/>
-      <c r="U3" s="17"/>
+      <c r="M3" s="29"/>
+      <c r="N3" s="29"/>
+      <c r="O3" s="29"/>
+      <c r="P3" s="29"/>
+      <c r="Q3" s="29"/>
+      <c r="R3" s="29"/>
+      <c r="S3" s="29"/>
+      <c r="T3" s="29"/>
+      <c r="U3" s="29"/>
     </row>
     <row r="4" spans="1:21" ht="23.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16" t="s">
-        <v>69</v>
-      </c>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
-      <c r="K4" s="16"/>
-      <c r="L4" s="16"/>
-      <c r="M4" s="16"/>
-      <c r="N4" s="16"/>
-      <c r="O4" s="16"/>
-      <c r="P4" s="16"/>
-      <c r="Q4" s="16"/>
-      <c r="R4" s="16"/>
-      <c r="S4" s="16"/>
-      <c r="T4" s="16"/>
-      <c r="U4" s="16"/>
+      <c r="A4" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="28"/>
+      <c r="M4" s="28"/>
+      <c r="N4" s="28"/>
+      <c r="O4" s="28"/>
+      <c r="P4" s="28"/>
+      <c r="Q4" s="28"/>
+      <c r="R4" s="28"/>
+      <c r="S4" s="28"/>
+      <c r="T4" s="28"/>
+      <c r="U4" s="28"/>
     </row>
     <row r="5" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="16"/>
-      <c r="M5" s="16"/>
-      <c r="N5" s="16"/>
-      <c r="O5" s="16"/>
-      <c r="P5" s="16"/>
-      <c r="Q5" s="16"/>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28"/>
+      <c r="P5" s="28"/>
+      <c r="Q5" s="28"/>
+      <c r="R5" s="28"/>
+      <c r="S5" s="28"/>
+      <c r="T5" s="28"/>
+      <c r="U5" s="28"/>
     </row>
     <row r="6" spans="1:21" ht="3" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="1:21" s="6" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="18" t="s">
+      <c r="A7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="18" t="s">
+      <c r="F7" s="23"/>
+      <c r="G7" s="23"/>
+      <c r="H7" s="17" t="s">
+        <v>11</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="25"/>
+      <c r="K7" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="23" t="s">
-        <v>13</v>
-      </c>
-      <c r="J7" s="24"/>
-      <c r="K7" s="18" t="s">
-        <v>16</v>
-      </c>
-      <c r="L7" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="M7" s="18" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="O7" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="P7" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q7" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="R7" s="18"/>
-      <c r="S7" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="T7" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="U7" s="27" t="s">
+      <c r="L7" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="M7" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="N7" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="O7" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="P7" s="17" t="s">
         <v>54</v>
+      </c>
+      <c r="Q7" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="R7" s="17"/>
+      <c r="S7" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="T7" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="U7" s="21" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:21" s="6" customFormat="1" ht="132" x14ac:dyDescent="0.3">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="21"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="27"/>
       <c r="E8" s="10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" s="10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="22"/>
+        <v>15</v>
+      </c>
+      <c r="H8" s="23"/>
       <c r="I8" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="J8" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="K8" s="19"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="19"/>
-      <c r="N8" s="19"/>
-      <c r="O8" s="19"/>
-      <c r="P8" s="19"/>
+      <c r="K8" s="18"/>
+      <c r="L8" s="18"/>
+      <c r="M8" s="18"/>
+      <c r="N8" s="18"/>
+      <c r="O8" s="18"/>
+      <c r="P8" s="18"/>
       <c r="Q8" s="10" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="R8" s="10" t="s">
-        <v>56</v>
-      </c>
-      <c r="S8" s="26"/>
-      <c r="T8" s="26"/>
-      <c r="U8" s="28"/>
+        <v>53</v>
+      </c>
+      <c r="S8" s="20"/>
+      <c r="T8" s="20"/>
+      <c r="U8" s="22"/>
     </row>
     <row r="9" spans="1:21" s="13" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="E9" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="F9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="12" t="s">
+      <c r="G9" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="H9" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="I9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="J9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="K9" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="L9" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="J9" s="12" t="s">
+      <c r="M9" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="K9" s="12" t="s">
+      <c r="N9" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="12" t="s">
+      <c r="O9" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="M9" s="12" t="s">
+      <c r="P9" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q9" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="N9" s="12" t="s">
+      <c r="R9" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="O9" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="P9" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q9" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="R9" s="12" t="s">
-        <v>51</v>
-      </c>
       <c r="S9" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="T9" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="U9" s="12" t="s">
         <v>58</v>
-      </c>
-      <c r="T9" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="U9" s="12" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:21" s="6" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="8" t="s">
+      <c r="F10" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="G10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="L10" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M10" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q10" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="R10" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="S10" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="K10" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="L10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M10" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="N10" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="O10" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="P10" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q10" s="9" t="s">
+      <c r="T10" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="R10" s="9" t="s">
+      <c r="U10" s="14" t="s">
         <v>65</v>
-      </c>
-      <c r="S10" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="T10" s="29" t="s">
-        <v>67</v>
-      </c>
-      <c r="U10" s="14" t="s">
-        <v>68</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="L2:U2"/>
+    <mergeCell ref="L3:U3"/>
+    <mergeCell ref="A4:U4"/>
+    <mergeCell ref="A5:U5"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="C7:C8"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="N7:N8"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
     <mergeCell ref="P7:P8"/>
     <mergeCell ref="Q7:R7"/>
     <mergeCell ref="S7:S8"/>
     <mergeCell ref="O7:O8"/>
     <mergeCell ref="U7:U8"/>
     <mergeCell ref="T7:T8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="N7:N8"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="B7:B8"/>
-    <mergeCell ref="C7:C8"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="L2:U2"/>
-    <mergeCell ref="L3:U3"/>
-    <mergeCell ref="A4:U4"/>
-    <mergeCell ref="A5:U5"/>
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A3:E3"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.6" right="0.5" top="0.6" bottom="0.5" header="0.05" footer="0.05"/>
